--- a/整合性チェック_部門別営業利益_第55期.xlsx
+++ b/整合性チェック_部門別営業利益_第55期.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="148">
   <si>
     <r>
       <rPr>
@@ -3009,6 +3009,925 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">部門別損益ファイルの更新</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・「部門別損益</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_FY202507-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">55</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_260604_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">加藤様</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Excel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">反映版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」として、タブ「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">202408-202507</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」の実績列（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B/E/H/K/N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列）のみ数値を更新。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">　数式・書式・レイアウトは一切変更していない（修正額①〜⑤は既存数式により自動再計算）。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・加藤様</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Excel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は「広告制作」「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DDG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">区分のみで部門内訳がないため、差異額は各区分内の部門の既存残高比で按分した：</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　　売上高　＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6,875</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円 → 企画制作＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5,445</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円／デジタル制作＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,430</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　　外注費　広告制作＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">168,945</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円 → 企画制作＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">104,727</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円／デジタル制作＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64,218</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　　　　　　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DDG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">49,823</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円 → ソリューション開発＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">47,063</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円／データベースマーケティング＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2,760</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　　旅費交通費　広告制作＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4,078</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円 → 全額企画制作／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DDG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">256,102</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円 → ソリューション開発＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">211,582</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">マーケ＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">44,520</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　　支払手数料　＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12,834</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円 → 企画制作＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10,359</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円／デジタル制作＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2,475</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　　朝日請求＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8,315</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円→企画制作、交際費＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3,704</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円・研修費＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3,710</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円→ソリューション開発（相手部門の残高が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のため）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・重要：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">p.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に表示される区分合計（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q/T/W</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列）および修正額は、上記の部門内按分の方法によらず一意に決まる。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　（システム利用料の配賦基準</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝広告制作売上＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">マーケ売上、地代家賃・共益費の配賦基準</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝対象</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">事業売上合計であり、</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　　いずれも区分内の内訳に依存しないため。）按分方法の変更は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部門別の内訳表示にのみ影響する。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・全社営業利益は△</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40,127,821</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円（賃料収入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13,200,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円を含む）となり、加藤様</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Excel△53,327,821</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円との差は</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　賃料収入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13,200,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円と完全一致（不動産賃貸事業は譲渡対象外のため加藤様</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Excel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">では対象外）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">未反映事項（要確認）</t>
     </r>
   </si>
@@ -3036,16 +3955,16 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">「財務ハイライト（部門別売上推移）」の広告制作売上高は企画制作</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">97,375</t>
+      <t xml:space="preserve">「財務ハイライト（部門別売上推移）」は未更新。上記按分によれば企画制作</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">97,380</t>
     </r>
     <r>
       <rPr>
@@ -3062,25 +3981,86 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">25,571</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">千円と部門別に</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　開示しているが、加藤様</t>
+      <t xml:space="preserve">25,573</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">千円</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　（合計</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">302,766</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">千円）となるが、＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6,875</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円の実際の帰属部門は加藤様にご確認いただく必要がある。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・共通部門の売上高△</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">708,100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円は加藤様</t>
     </r>
     <r>
       <rPr>
@@ -3097,68 +4077,262 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">の広告制作売上高は</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">122,952,993</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円（＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6,875</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円）であり、両部門への内訳が不明のため未更新。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　同スライドを更新する場合は、＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6,875</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円の帰属部門を加藤様にご確認いただく必要がある。</t>
+      <t xml:space="preserve">に基づき反映したが、内容（売上値引・返金等）は未確認。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　譲渡対象</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">事業の数値には影響しない。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">既存ファイルの既知の不具合（今回の更新とは無関係）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・タブ「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">202208-12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">検証用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2_diff</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」は参照先シートが削除済みのため全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">980</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">セルが参照エラー（＃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">REF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">！）。原本から同一の状態。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・企業概要書</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.pptx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のスライド</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">34</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は画像リレーションが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Target="NULL"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で破損。原本から同一の状態。</t>
     </r>
   </si>
 </sst>
@@ -7100,7 +8274,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -7238,6 +8412,120 @@
       <c r="A23" s="5"/>
       <c r="B23" s="21" t="s">
         <v>128</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5"/>
+      <c r="B24" s="21" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5"/>
+      <c r="B25" s="21" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5"/>
+      <c r="B26" s="21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5"/>
+      <c r="B27" s="21" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5"/>
+      <c r="B28" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5"/>
+      <c r="B29" s="21" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5"/>
+      <c r="B30" s="21" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5"/>
+      <c r="B31" s="21" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5"/>
+      <c r="B32" s="21" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5"/>
+      <c r="B33" s="21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5"/>
+      <c r="B34" s="21" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="B35" s="21"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5"/>
+      <c r="B36" s="21" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5"/>
+      <c r="B37" s="21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5"/>
+      <c r="B38" s="21" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5"/>
+      <c r="B39" s="21" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="B40" s="21"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5"/>
+      <c r="B41" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5"/>
+      <c r="B42" s="21" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
